--- a/vendor_application_form_templates/007_lash_training_center_partnership_application_form--vendor_application_form_templates.xlsx
+++ b/vendor_application_form_templates/007_lash_training_center_partnership_application_form--vendor_application_form_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -642,8 +642,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'vendor',_'value':_'lash_training_center'}</t>
+          <t>lash_training_center</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'vendor', 'value': 'Lash Training Center'}</t>
+          <t>Lash Training Center</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'contact_person',_'value':_'jimmy_chen'}</t>
+          <t>jimmy_chen</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'contact_person', 'value': 'Jimmy Chen'}</t>
+          <t>Jimmy Chen</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'contact_email',_'value':_'example@example.com'}</t>
+          <t>example@example.com</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'contact_email', 'value': 'example@example.com'}</t>
+          <t>example@example.com</t>
         </is>
       </c>
     </row>
@@ -722,12 +722,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'contact_phone',_'value':_'123-456-7890'}</t>
+          <t>123-456-7890</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'contact_phone', 'value': '123-456-7890'}</t>
+          <t>123-456-7890</t>
         </is>
       </c>
     </row>
@@ -739,12 +739,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'contact_address',_'value':_'123_street'}</t>
+          <t>123_street</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'contact_address', 'value': '123 Street'}</t>
+          <t>123 Street</t>
         </is>
       </c>
     </row>
@@ -756,12 +756,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'partnership_type',_'value':_'partnership_type'}</t>
+          <t>partnership_type</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'partnership_type', 'value': 'Partnership Type'}</t>
+          <t>Partnership Type</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'partnership_location',_'value':_'partnership_location'}</t>
+          <t>partnership_location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'partnership_location', 'value': 'Partnership Location'}</t>
+          <t>Partnership Location</t>
         </is>
       </c>
     </row>
@@ -790,12 +790,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'partnership_start_date',_'value':_'start_date'}</t>
+          <t>start_date</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'partnership_start_date', 'value': 'Start Date'}</t>
+          <t>Start Date</t>
         </is>
       </c>
     </row>
